--- a/poster-run/waypoint-flyer-run.xlsx
+++ b/poster-run/waypoint-flyer-run.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="296">
   <si>
     <t xml:space="preserve">Waypoint flyers</t>
   </si>
@@ -825,7 +825,7 @@
     <t xml:space="preserve">Print list</t>
   </si>
   <si>
-    <t xml:space="preserve">Counts update from the 'All stops (route)' sheet. Change the blue numbers if you want more or fewer per stop.</t>
+    <t xml:space="preserve">Counts update from the 'All stops (route)' sheet. Change the blue numbers for more or fewer per stop, or more spares. Page numbers are in waypoint-flyers-print.pdf.</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -837,6 +837,9 @@
     <t xml:space="preserve">Per stop</t>
   </si>
   <si>
+    <t xml:space="preserve">Spares</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pieces</t>
   </si>
   <si>
@@ -849,28 +852,46 @@
     <t xml:space="preserve">Paper</t>
   </si>
   <si>
-    <t xml:space="preserve">Waypoint flyer (Letter)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cardstock or paper. Spare +5 for torn ones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waypoint counter cards (half-letter)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cardstock. Cut in half on the line.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apps poster (Letter)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paper is fine on boards.</t>
+    <t xml:space="preserve">Sides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waypoint flyer A or B (Letter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-sided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain copy paper. PDF page 1 (A) or 2 (B).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waypoint counter cards (quarter-letter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardstock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-sided, flip on long edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF pages 3 (front) and 4 (back). Cut on the dashed lines into 4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apps poster A or B (Letter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper is fine on boards. PDF page 5 (A) or 6 (B).</t>
   </si>
   <si>
     <t xml:space="preserve">Apps take-one cards (quarter-letter)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cardstock. Cut on the crop marks.</t>
+    <t xml:space="preserve">Cut on the crop marks. PDF page 7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardstock sheets (65 lb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy paper sheets</t>
   </si>
   <si>
     <t xml:space="preserve">Total sheets</t>
@@ -889,6 +910,9 @@
   </si>
   <si>
     <t xml:space="preserve">• Ask first everywhere. Boards get cleared every 2–4 weeks, so re-post on the 1st of each month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter cards print on both sides: see 'How to print two-sided' in poster-run/README.md. Print one test sheet first.</t>
   </si>
   <si>
     <t xml:space="preserve">Addresses and hours come from Google Maps and earlier route notes (Oct 2026). Check hours before a long drive.</t>
@@ -901,7 +925,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -971,6 +995,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF12252F"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1047,7 +1079,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1092,10 +1124,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1104,11 +1132,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6173,14 +6209,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6193,170 +6232,238 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="5" t="s">
         <v>272</v>
       </c>
+      <c r="H4" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" s="12" t="n">
+      <c r="A5" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('All stops (route)'!G5:G65,"*Waypoint flyer*")</f>
         <v>10</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="n">
-        <f aca="false">B5*C5</f>
-        <v>10</v>
-      </c>
-      <c r="E5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <f aca="false">B5*C5+D5</f>
+        <v>12</v>
+      </c>
+      <c r="F5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <f aca="false">ROUNDUP(D5/E5,0)</f>
-        <v>10</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="G5" s="4" t="n">
+        <f aca="false">ROUNDUP(E5/F5,0)</f>
+        <v>12</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('All stops (route)'!G5:G65,"*Waypoint counter cards*")</f>
         <v>26</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="12" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="12" t="n">
-        <f aca="false">B6*C6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <f aca="false">B6*C6+D6</f>
         <v>156</v>
       </c>
-      <c r="E6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <f aca="false">ROUNDUP(D6/E6,0)</f>
-        <v>78</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>276</v>
+      <c r="F6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <f aca="false">ROUNDUP(E6/F6,0)</f>
+        <v>39</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="A7" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('All stops (route)'!G5:G65,"*Apps poster*")</f>
         <v>21</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="12" t="n">
-        <f aca="false">B7*C7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <f aca="false">B7*C7+D7</f>
         <v>21</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="F7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <f aca="false">ROUNDUP(D7/E7,0)</f>
+      <c r="G7" s="4" t="n">
+        <f aca="false">ROUNDUP(E7/F7,0)</f>
         <v>21</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>278</v>
+      <c r="H7" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B8" s="12" t="n">
+      <c r="A8" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('All stops (route)'!G5:G65,"*Apps take-one cards*")</f>
         <v>21</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="12" t="n">
-        <f aca="false">B8*C8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <f aca="false">B8*C8+D8</f>
         <v>168</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="F8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <f aca="false">ROUNDUP(D8/E8,0)</f>
+      <c r="G8" s="4" t="n">
+        <f aca="false">ROUNDUP(E8/F8,0)</f>
         <v>42</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>280</v>
+      <c r="H8" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <f aca="false">SUM(F5:F8)</f>
-        <v>151</v>
+        <v>286</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <f aca="false">SUMIF(H5:H8,"Cardstock",G5:G8)</f>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <f aca="false">SUMIF(H5:H8,"Paper",G5:G8)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <f aca="false">G10+G11</f>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>284</v>
+      <c r="A14" s="14" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>285</v>
+      <c r="A15" s="11" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>286</v>
+      <c r="A16" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>287</v>
+      <c r="A18" s="11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
